--- a/naver-place-crawler/results_hair/판교_미용실.xlsx
+++ b/naver-place-crawler/results_hair/판교_미용실.xlsx
@@ -426,7 +426,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,24 +564,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>궁서채 판교점</t>
+          <t>더레드도어헤어 대장동미용실</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dmlgml76@naver.com</t>
+          <t>090902_love@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1440-2894</t>
+          <t>0507-1446-1544</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로255번길 9-22 210호</t>
+          <t>경기도 성남시 분당구 판교대장로 92 푸리마타워 3층 304호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>917</v>
+        <v>1402</v>
       </c>
       <c r="Q2" t="n">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1134</v>
+        <v>1406</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1508959519</t>
+          <t>1122198740</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1508959519</t>
+          <t>https://m.place.naver.com/place/1122198740</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>세르담</t>
+          <t>꾸아퍼스트 현대백화점 판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lllyunjin@naver.com</t>
+          <t>eheh1008@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-705-0501</t>
+          <t>0507-1359-3242</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 6-3 1층 102호</t>
+          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 10층 꾸아퍼스트</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://smartstore.naver.com/coiff1rst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>161</v>
+        <v>5143</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="R3" t="n">
-        <v>181</v>
+        <v>5231</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2098377967</t>
+          <t>37053146</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098377967</t>
+          <t>https://m.place.naver.com/place/37053146</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>도헤어룸</t>
+          <t>비르덴 맨즈헤어</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tfg3270@naver.com</t>
+          <t>virdenhair@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1334-4063</t>
+          <t>0507-1423-2452</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로5길 20 119호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역(7-1BL) 판매시설 지2층 B2108호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kimdoyoung1004</t>
+          <t>https://www.instagram.com/virden_hojin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>89</v>
+        <v>211</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1403451973</t>
+          <t>2019148915</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403451973</t>
+          <t>https://m.place.naver.com/place/2019148915</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>꾸아퍼스트 현대백화점 판교점</t>
+          <t>우브헤어</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eheh1008@naver.com</t>
+          <t>qazwsx159925@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1359-3242</t>
+          <t>0507-1334-6341</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로146번길 20 현대백화점 10층 꾸아퍼스트</t>
+          <t>경기도 성남시 분당구 판교대장로7길 6-1 101호 우브헤어</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/coiff1rst</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>5136</v>
+        <v>740</v>
       </c>
       <c r="Q5" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="R5" t="n">
-        <v>5225</v>
+        <v>766</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37053146</t>
+          <t>1080085479</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37053146</t>
+          <t>https://m.place.naver.com/place/1080085479</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뮤니아헤어</t>
+          <t>에이엔노</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>knowles2334@naver.com</t>
+          <t>eienno_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1341-0158</t>
+          <t>0507-1426-9150</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로125번길 9 1층 101호</t>
+          <t>경기도 성남시 분당구 판교역로14번길 16 민프라자 106호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hairshop_eienno/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>185</v>
+        <v>94</v>
       </c>
       <c r="Q6" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2039532912</t>
+          <t>1194861463</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039532912</t>
+          <t>https://m.place.naver.com/place/1194861463</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1034,39 +1034,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여기지금헤어 분당판교점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>hairsalon-h_n@naver.com</t>
-        </is>
-      </c>
+          <t>뮤니아헤어</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1303-3453</t>
+          <t>0507-1341-0158</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 178 서건타워 6층 604호</t>
+          <t>경기도 성남시 분당구 운중로125번길 9 1층 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xbjxjhxb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1082,22 +1078,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4651</v>
+        <v>191</v>
       </c>
       <c r="Q7" t="n">
-        <v>421</v>
+        <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>5072</v>
+        <v>241</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1895530050</t>
+          <t>2039532912</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895530050</t>
+          <t>https://m.place.naver.com/place/2039532912</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바이아티 판교점</t>
+          <t>헤어이즈엠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>byarti@naver.com</t>
+          <t>eensy90@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1353-1085</t>
+          <t>0507-1439-4180</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로1길 26-6 1층 바이아티 판교점</t>
+          <t>경기도 성남시 분당구 판교역로 240 A동 지하1층 B123-1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/byarti</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,12 +1156,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1521</v>
+        <v>247</v>
       </c>
       <c r="Q8" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="R8" t="n">
-        <v>1581</v>
+        <v>335</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1642532161</t>
+          <t>1240454467</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1642532161</t>
+          <t>https://m.place.naver.com/place/1240454467</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>온니브헤어 판교점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>reinforce3920@naver.com</t>
-        </is>
-      </c>
+          <t>아센티 더 판교</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1380-6880</t>
+          <t>0507-1342-4783</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 211호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 10 라스트리트 타워 1동 2층 212호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reinforce3920</t>
+          <t>https://www.instagram.com/asenti_the_pangyo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1208</v>
+        <v>961</v>
       </c>
       <c r="Q9" t="n">
-        <v>321</v>
+        <v>63</v>
       </c>
       <c r="R9" t="n">
-        <v>1529</v>
+        <v>1024</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1269991341</t>
+          <t>1693297113</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1269991341</t>
+          <t>https://m.place.naver.com/place/1693297113</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1308,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>꼼나나비앙 판교점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>comme_pangyo@naver.com</t>
-        </is>
-      </c>
+          <t>궁서채 판교점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1332-8195</t>
+          <t>0507-1440-2894</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 10 라스트리트 1동 2층 224호</t>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 210호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/commenanabien_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,7 +1336,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1369,17 +1357,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5891</v>
+        <v>922</v>
       </c>
       <c r="Q10" t="n">
-        <v>362</v>
+        <v>217</v>
       </c>
       <c r="R10" t="n">
-        <v>6253</v>
+        <v>1139</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1867649955</t>
+          <t>1508959519</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867649955</t>
+          <t>https://m.place.naver.com/place/1508959519</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1398,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 동판교H스퀘어점</t>
+          <t>나이스가이 백현마을점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wodus8449@naver.com</t>
+          <t>jungwoo4094600@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1439-7713</t>
+          <t>031-707-0705</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 235 에이치스퀘어 N동 지하1층 B112호</t>
+          <t>경기도 성남시 분당구 동판교로 59 판교자유퍼스트프라자1 1층 107호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pg_no1_master</t>
+          <t>http://www.iniceguy.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,7 +1435,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3785</v>
+        <v>141</v>
       </c>
       <c r="Q11" t="n">
-        <v>833</v>
+        <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>4618</v>
+        <v>167</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>21025040</t>
+          <t>1806062147</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21025040</t>
+          <t>https://m.place.naver.com/place/1806062147</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1504,44 +1492,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>와이오유 판교점</t>
+          <t>연청살롱</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>i95kitty@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>7uoknow7@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1406-1479</t>
+          <t>031-707-0426</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로18번길 18</t>
+          <t>경기도 성남시 분당구 운중로 255 101호 연청살롱</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/c/와이오유yousalon</t>
+          <t>https://booking.naver.com/booking/13/bizes/511640</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,17 +1549,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10042</v>
+        <v>1126</v>
       </c>
       <c r="Q12" t="n">
-        <v>808</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>10850</v>
+        <v>1129</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>35194802</t>
+          <t>1930679218</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35194802</t>
+          <t>https://m.place.naver.com/place/1930679218</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1590,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>준오헤어 서판교점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lowing1018@naver.com</t>
-        </is>
-      </c>
+          <t>헤어마드 판교점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1332-0610</t>
+          <t>0507-1342-6828</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 249 더제이에스빌딩 2층 준오헤어 서판교점</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 지1층 비107호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/junospg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1630,7 +1618,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1651,17 +1639,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>13074</v>
+        <v>1136</v>
       </c>
       <c r="Q13" t="n">
-        <v>476</v>
+        <v>62</v>
       </c>
       <c r="R13" t="n">
-        <v>13550</v>
+        <v>1198</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1391913826</t>
+          <t>1640957766</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391913826</t>
+          <t>https://m.place.naver.com/place/1640957766</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1680,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>닥터</t>
+          <t>누크헤어</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_h0402_@naver.com</t>
+          <t>102938az@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1404-7739</t>
+          <t>0507-1315-8642</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩</t>
+          <t>경기도 성남시 분당구 판교역로 136 판교역 힐스테이트 지하2층 블루존 B2013,2014호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/h_h0402_</t>
+          <t>https://www.instagram.com/suhos1n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1729,7 +1717,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1745,17 +1733,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>742</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>742</v>
+        <v>154</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>741268087</t>
+          <t>1017849823</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/741268087</t>
+          <t>https://m.place.naver.com/place/1017849823</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1774,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>예온헤어</t>
+          <t>차홍룸 판교점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sia1245@naver.com</t>
+          <t>chahong1@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1364-0551</t>
+          <t>0507-1337-4752</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로113번길 4-15 1층 예온헤어</t>
+          <t>경기도 성남시 분당구 판교역로 136 상가1층 1105호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_ye.on___</t>
+          <t>https://www.facebook.com/chahongofficial</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1823,7 +1811,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1843,13 +1831,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>630</v>
+        <v>14136</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>303</v>
       </c>
       <c r="R15" t="n">
-        <v>660</v>
+        <v>14439</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,17 +1846,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1912135190</t>
+          <t>1617942139</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912135190</t>
+          <t>https://m.place.naver.com/place/1617942139</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1880,29 +1868,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>리미띠에헤어 분당판교점</t>
+          <t>유하헤어 이매점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>limitie22@naver.com</t>
+          <t>u_hahair@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1408-2150</t>
+          <t>0507-1453-1580</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층</t>
+          <t>경기도 성남시 분당구 성남대로779번길 52 1층 109호, 110호, 111호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/limitie_/</t>
+          <t>https://blog.naver.com/u_hahair</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1917,7 +1905,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1933,17 +1921,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2092</v>
+        <v>835</v>
       </c>
       <c r="Q16" t="n">
-        <v>4710</v>
+        <v>42</v>
       </c>
       <c r="R16" t="n">
-        <v>6802</v>
+        <v>877</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,17 +1940,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1490723364</t>
+          <t>1873348000</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490723364</t>
+          <t>https://m.place.naver.com/place/1873348000</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1974,29 +1962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>태브로 헤어살롱</t>
+          <t>미노크 판교 라이브러리</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>taebro6600@naver.com</t>
+          <t>jtmina@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>031-8017-6600</t>
+          <t>0507-1408-4669</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로25번길 6-8 1층</t>
+          <t>경기도 성남시 분당구 판교공원로1길 18-1 1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/taebro6600</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2006,12 +1994,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2027,17 +2015,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>242</v>
+        <v>890</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="R17" t="n">
-        <v>300</v>
+        <v>1015</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2034,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>36073460</t>
+          <t>1089065440</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36073460</t>
+          <t>https://m.place.naver.com/place/1089065440</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에이엔노</t>
+          <t>너란헤어</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>eienno_@naver.com</t>
+          <t>2jonga@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1426-9150</t>
+          <t>0507-1330-3363</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로14번길 16 민프라자 106호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 6-8 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hairshop_eienno/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2100,7 +2088,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2121,17 +2109,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>89</v>
+        <v>746</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="R18" t="n">
-        <v>107</v>
+        <v>798</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2128,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1194861463</t>
+          <t>1408351227</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1194861463</t>
+          <t>https://m.place.naver.com/place/1408351227</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2162,29 +2150,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>헤리안</t>
+          <t>바이아티 판교점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>berrytaste@naver.com</t>
+          <t>byarti@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1381-7970</t>
+          <t>0507-1353-1085</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 235 N동 1층 129호</t>
+          <t>경기도 성남시 분당구 판교공원로1길 26-6 1층 바이아티 판교점</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/herian_official</t>
+          <t>https://blog.naver.com/byarti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2199,7 +2187,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2219,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>573</v>
+        <v>1569</v>
       </c>
       <c r="Q19" t="n">
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="R19" t="n">
-        <v>743</v>
+        <v>1630</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1327869349</t>
+          <t>1642532161</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327869349</t>
+          <t>https://m.place.naver.com/place/1642532161</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2256,25 +2244,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>아뜰리에조이</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>hyju0313@naver.com</t>
-        </is>
-      </c>
+          <t>박승철헤어스투디오 동판교H스퀘어점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1439-7713</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 산운로160번길 20-5 1층 101호</t>
+          <t>경기도 성남시 분당구 판교역로 235 에이치스퀘어 N동 지하1층 B112호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://instagram.com/atelier.joy_</t>
+          <t>https://www.instagram.com/pg_no1_master</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2309,13 +2297,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>434</v>
+        <v>3804</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>863</v>
       </c>
       <c r="R20" t="n">
-        <v>450</v>
+        <v>4667</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2312,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1708579651</t>
+          <t>21025040</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708579651</t>
+          <t>https://m.place.naver.com/place/21025040</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2346,29 +2334,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>와이디헤어 판교점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>yd_siyeon@naver.com</t>
-        </is>
-      </c>
+          <t>뭍 판교점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>031-703-4143</t>
+          <t>0507-1363-3974</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로146번길 35-8 1층 102호</t>
+          <t>경기도 성남시 분당구 판교역로 136 중앙광장 1층 1067호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yd__official</t>
+          <t>https://www.instagram.com/woojin.d</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2403,13 +2387,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>504</v>
+        <v>1064</v>
       </c>
       <c r="Q21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R21" t="n">
-        <v>553</v>
+        <v>1114</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,51 +2402,51 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1499829661</t>
+          <t>1081078030</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1499829661</t>
+          <t>https://m.place.naver.com/place/1081078030</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>더레브 맨즈헤어</t>
+          <t>연월 헤어</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>therevemenshair@naver.com</t>
+          <t>mimimomarket@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1380-8288</t>
+          <t>031-703-2369</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로18번길 8 1층</t>
+          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 202호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jin__reve</t>
+          <t>http://www.instagram.com/misty_moonlight_hair</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2497,13 +2481,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2980</v>
+        <v>834</v>
       </c>
       <c r="Q22" t="n">
-        <v>532</v>
+        <v>266</v>
       </c>
       <c r="R22" t="n">
-        <v>3512</v>
+        <v>1100</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2496,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1290685047</t>
+          <t>1535596046</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290685047</t>
+          <t>https://m.place.naver.com/place/1535596046</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2534,29 +2518,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아티스틱 판교점</t>
+          <t>와이디헤어 판교점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sxbapribfn796@naver.com</t>
+          <t>yd_siyeon@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1452-9191</t>
+          <t>031-703-4143</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 2층 아티스틱 판교점</t>
+          <t>경기도 성남시 분당구 운중로146번길 35-8 1층 102호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artistichair_</t>
+          <t>https://www.instagram.com/yd__official</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2591,13 +2575,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2713</v>
+        <v>519</v>
       </c>
       <c r="Q23" t="n">
-        <v>595</v>
+        <v>50</v>
       </c>
       <c r="R23" t="n">
-        <v>3308</v>
+        <v>569</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,17 +2590,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>37997378</t>
+          <t>1499829661</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37997378</t>
+          <t>https://m.place.naver.com/place/1499829661</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2628,29 +2612,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>궁서채 서현역점</t>
+          <t>온니브헤어 판교점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>muadhair@naver.com</t>
+          <t>reinforce3920@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1467-2069</t>
+          <t>0507-1380-6880</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 3층 302호 궁서채 서현역점</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 211호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/muadhair</t>
+          <t>https://blog.naver.com/reinforce3920</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2685,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>401</v>
+        <v>1230</v>
       </c>
       <c r="Q24" t="n">
-        <v>1275</v>
+        <v>321</v>
       </c>
       <c r="R24" t="n">
-        <v>1676</v>
+        <v>1551</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,51 +2684,51 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1278312550</t>
+          <t>1269991341</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1278312550</t>
+          <t>https://m.place.naver.com/place/1269991341</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>온맨즈헤어 판교역점</t>
+          <t>에이치플레이스 그레이츠판교역점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>onmanshair@naver.com</t>
+          <t>woosy0225@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1439-0378</t>
+          <t>0507-1320-5923</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 1층 40호</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 그레이츠 판교 2층 201-2호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onmanshair?tab=1&amp;trackingCode=blog_feed_mobile</t>
+          <t>https://www.instagram.com/h.place_official</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2759,7 +2743,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2779,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>201</v>
+        <v>6156</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>676</v>
       </c>
       <c r="R25" t="n">
-        <v>215</v>
+        <v>6832</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,17 +2778,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1243795094</t>
+          <t>1774601367</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243795094</t>
+          <t>https://m.place.naver.com/place/1774601367</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2816,29 +2800,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>준오헤어 판교아브뉴프랑점</t>
+          <t>토니앤가이 판교점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dlwnsrl48@naver.com</t>
+          <t>hair121212@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1496-5646</t>
+          <t>031-703-7577</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 2층 238호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/juno_pangyoaf</t>
+          <t>https://blog.naver.com/hair121212</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2853,7 +2837,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2869,17 +2853,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3258</v>
+        <v>4248</v>
       </c>
       <c r="Q26" t="n">
-        <v>1388</v>
+        <v>181</v>
       </c>
       <c r="R26" t="n">
-        <v>4646</v>
+        <v>4429</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,17 +2872,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2092451717</t>
+          <t>1891585241</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2092451717</t>
+          <t>https://m.place.naver.com/place/1891585241</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2910,29 +2894,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>이가자헤어비스 동판교점</t>
+          <t>리메이크헤어 판교점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lkjdpg@naver.com</t>
+          <t>remakehair@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-8016-8322</t>
+          <t>0507-1406-3654</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 메가스페이스 2층</t>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 308, 309호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lkjdpg</t>
+          <t>https://blog.naver.com/remakehair</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2967,13 +2951,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3520</v>
+        <v>1951</v>
       </c>
       <c r="Q27" t="n">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="R27" t="n">
-        <v>3887</v>
+        <v>2030</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,17 +2966,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37171597</t>
+          <t>953344394</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37171597</t>
+          <t>https://m.place.naver.com/place/953344394</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3004,29 +2988,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>꾸밈 판교역점</t>
+          <t>세르담</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jooa_design@naver.com</t>
+          <t>lllyunjin@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>031-702-7700</t>
+          <t>031-705-0501</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 180 2층 201호 꾸밈 판교역점</t>
+          <t>경기도 성남시 분당구 판교역로 6-3 1층 102호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jooa_design</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3036,12 +3020,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3057,17 +3041,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3741</v>
+        <v>165</v>
       </c>
       <c r="Q28" t="n">
-        <v>1705</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
-        <v>5446</v>
+        <v>187</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,17 +3060,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1107338199</t>
+          <t>2098377967</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107338199</t>
+          <t>https://m.place.naver.com/place/2098377967</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3098,29 +3082,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>리메이크헤어 판교점</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>remakehair@naver.com</t>
-        </is>
-      </c>
+          <t>미노크 판교 본점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1406-3654</t>
+          <t>0507-1393-4669</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 308, 309호</t>
+          <t>경기도 성남시 분당구 판교공원로3길 18 1층 102호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/remakehair</t>
+          <t>https://www.instagram.com/menoke.official/?igshid=YmMyMTA2M2Y%3D</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3135,7 +3115,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3151,17 +3131,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1946</v>
+        <v>2189</v>
       </c>
       <c r="Q29" t="n">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="R29" t="n">
-        <v>2025</v>
+        <v>2329</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,17 +3150,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>953344394</t>
+          <t>1260361427</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/953344394</t>
+          <t>https://m.place.naver.com/place/1260361427</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3192,29 +3172,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>너란헤어</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2jonga@naver.com</t>
-        </is>
-      </c>
+          <t>준오헤어 판교아브뉴프랑점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1330-3363</t>
+          <t>0507-1496-5646</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 6-8 1층</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 2층 238호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/juno_pangyoaf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3224,7 +3200,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3245,17 +3221,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>748</v>
+        <v>3443</v>
       </c>
       <c r="Q30" t="n">
-        <v>52</v>
+        <v>1435</v>
       </c>
       <c r="R30" t="n">
-        <v>800</v>
+        <v>4878</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,51 +3240,51 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1408351227</t>
+          <t>2092451717</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1408351227</t>
+          <t>https://m.place.naver.com/place/2092451717</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>유하헤어 이매점</t>
+          <t>온맨즈헤어 판교역점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>u_hahair@naver.com</t>
+          <t>onmanshair@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1453-1580</t>
+          <t>0507-1439-0378</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 52 1층 109호, 110호, 111호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 1층 40호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/u_hahair</t>
+          <t>https://blog.naver.com/onmanshair?tab=1&amp;trackingCode=blog_feed_mobile</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3339,17 +3315,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>819</v>
+        <v>211</v>
       </c>
       <c r="Q31" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="R31" t="n">
-        <v>860</v>
+        <v>225</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3358,17 +3334,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1873348000</t>
+          <t>1243795094</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1873348000</t>
+          <t>https://m.place.naver.com/place/1243795094</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3380,29 +3356,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아이디헤어 분당수내점</t>
+          <t>태브로 헤어살롱</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>idhairsunae@naver.com</t>
+          <t>taebro6600@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1407-0805</t>
+          <t>031-8017-6600</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 21 풍해빌딩 2층</t>
+          <t>경기도 성남시 분당구 판교로25번길 6-8 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/idhairsunae</t>
+          <t>https://blog.naver.com/taebro6600</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3437,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>17313</v>
+        <v>244</v>
       </c>
       <c r="Q32" t="n">
-        <v>972</v>
+        <v>58</v>
       </c>
       <c r="R32" t="n">
-        <v>18285</v>
+        <v>302</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3452,17 +3428,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>35240005</t>
+          <t>36073460</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35240005</t>
+          <t>https://m.place.naver.com/place/36073460</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3474,29 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>에쉬비헤어</t>
+          <t>순수 더블트리 바이 힐튼 서울 판교점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>achevee@naver.com</t>
+          <t>dkfk2685@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1351-6260</t>
+          <t>0507-1305-1379</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 65 1층 102호</t>
+          <t>경기도 성남시 분당구 백현로 26 레지던스동 G층 3호 순수 미용실</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/achevee</t>
+          <t>https://www.instagram.com/soonsoo_hilton</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3511,7 +3487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3527,17 +3503,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>879</v>
+        <v>312</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="R33" t="n">
-        <v>918</v>
+        <v>422</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3546,17 +3522,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1370317722</t>
+          <t>1403230950</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370317722</t>
+          <t>https://m.place.naver.com/place/1403230950</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3568,29 +3544,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>뭍 판교점</t>
+          <t>고이비헤어</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>bbolm@naver.com</t>
+          <t>qp6409@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1363-3974</t>
+          <t>0507-1448-3694</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 중앙광장 1층 1067호</t>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 A동 1층 115호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woojin.d</t>
+          <t>https://www.instagram.com/goibe_da_0000</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3625,13 +3601,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1042</v>
+        <v>260</v>
       </c>
       <c r="Q34" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1091</v>
+        <v>266</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3640,17 +3616,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1081078030</t>
+          <t>1172147949</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1081078030</t>
+          <t>https://m.place.naver.com/place/1172147949</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3662,34 +3638,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>시유헤어스튜디오</t>
+          <t>헤어하우스606 판교역점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hello_ngji@naver.com</t>
+          <t>jse0981@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1491-7920</t>
+          <t>0507-1333-7268</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 53 1층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오월드마크 상가동 1층 1-58호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sssean_11</t>
+          <t>http://pf.kakao.com/_JWuxdn/chat</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3710,22 +3686,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>124</v>
+        <v>339</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="R35" t="n">
-        <v>125</v>
+        <v>384</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3734,17 +3710,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2075127898</t>
+          <t>1005163873</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075127898</t>
+          <t>https://m.place.naver.com/place/1005163873</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3756,29 +3732,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>르모아</t>
+          <t>보니따라움</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>remonjoau@naver.com</t>
+          <t>socoolar@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>031-702-8797</t>
+          <t>0507-1426-4648</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로25번길 22-2 1층 르모아</t>
+          <t>경기도 성남시 분당구 판교역로2번길 17 1층 보니따라움</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/socoolar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3788,12 +3764,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3809,17 +3785,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3017</v>
+        <v>3072</v>
       </c>
       <c r="Q36" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="R36" t="n">
-        <v>3153</v>
+        <v>3191</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3828,17 +3804,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1943090935</t>
+          <t>1663607000</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1943090935</t>
+          <t>https://m.place.naver.com/place/1663607000</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3850,29 +3826,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>연월 헤어</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>mimimomarket@naver.com</t>
-        </is>
-      </c>
+          <t>아티스틱 판교점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>031-703-2369</t>
+          <t>0507-1452-9191</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 129 마크시티옐로우빌딩 202호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 2층 아티스틱 판교점</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/misty_moonlight_hair</t>
+          <t>https://www.instagram.com/artistichair_</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3907,13 +3879,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>832</v>
+        <v>2718</v>
       </c>
       <c r="Q37" t="n">
-        <v>267</v>
+        <v>629</v>
       </c>
       <c r="R37" t="n">
-        <v>1099</v>
+        <v>3347</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3922,17 +3894,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1535596046</t>
+          <t>37997378</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535596046</t>
+          <t>https://m.place.naver.com/place/37997378</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3944,44 +3916,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이철헤어커커 동판교테크노점</t>
+          <t>와이오유 헤어 분당점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kerker2327@naver.com</t>
+          <t>songok82@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1423-2326</t>
+          <t>0507-1370-0256</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 376 마크시티퍼플 3층</t>
+          <t>경기도 성남시 분당구 백현로 100 정자 아이파크 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://leechulhairkerker.co.kr/</t>
+          <t>http://www.instagram.com/y.o.u_salon</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3992,7 +3964,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4001,13 +3973,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2006</v>
+        <v>10957</v>
       </c>
       <c r="Q38" t="n">
-        <v>95</v>
+        <v>510</v>
       </c>
       <c r="R38" t="n">
-        <v>2101</v>
+        <v>11467</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4016,51 +3988,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>36465836</t>
+          <t>1661978943</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36465836</t>
+          <t>https://m.place.naver.com/place/1661978943</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>립헤어</t>
+          <t>더레브 맨즈헤어</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>libbhair@naver.com</t>
+          <t>therevemenshair@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1493-0503</t>
+          <t>0507-1380-8288</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로5길 28 1층 립헤어</t>
+          <t>경기도 성남시 분당구 판교역로18번길 8 1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/libb_hair</t>
+          <t>https://www.instagram.com/jin__reve</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4095,13 +4067,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2187</v>
+        <v>2988</v>
       </c>
       <c r="Q39" t="n">
-        <v>233</v>
+        <v>532</v>
       </c>
       <c r="R39" t="n">
-        <v>2420</v>
+        <v>3520</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4110,17 +4082,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1564288288</t>
+          <t>1290685047</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564288288</t>
+          <t>https://m.place.naver.com/place/1290685047</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4132,34 +4104,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>예인헤어</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>anyjeonghwa@naver.com</t>
-        </is>
-      </c>
+          <t>바이모모헤어</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1325-2333</t>
+          <t>0507-1381-7525</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 393 이지더원아파트정문 상가 114호 예인헤어</t>
+          <t>경기도 성남시 분당구 판교대장로7길 5-25 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61574752066785</t>
+          <t>https://www.instagram.com/by.momo_hair</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4169,7 +4137,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4189,13 +4157,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>927</v>
+        <v>1846</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="R40" t="n">
-        <v>929</v>
+        <v>1889</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4204,17 +4172,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>36768398</t>
+          <t>1431660531</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36768398</t>
+          <t>https://m.place.naver.com/place/1431660531</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4226,29 +4194,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>바이모모헤어</t>
+          <t>제니스튜디오 판교점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>yejumeju@naver.com</t>
+          <t>dkyun22@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1381-7525</t>
+          <t>0507-1385-8458</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 5-25 1층</t>
+          <t>경기도 성남시 분당구 판교역로10번길 10-4 1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/by.momo_hair</t>
+          <t>https://blog.naver.com/dkyun22</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4263,7 +4231,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4283,13 +4251,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1831</v>
+        <v>2369</v>
       </c>
       <c r="Q41" t="n">
-        <v>43</v>
+        <v>829</v>
       </c>
       <c r="R41" t="n">
-        <v>1874</v>
+        <v>3198</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4298,17 +4266,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1431660531</t>
+          <t>1480897275</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431660531</t>
+          <t>https://m.place.naver.com/place/1480897275</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4320,34 +4288,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>공시하 판교점</t>
+          <t>여기지금헤어 분당판교점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>gongsiha@naver.com</t>
+          <t>hairsalon-h_n@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1349-7513</t>
+          <t>0507-1303-3453</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로1길 47 1층 공시하</t>
+          <t>경기도 성남시 분당구 판교역로 178 서건타워 6층 604호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gongsiha/223367774442</t>
+          <t>http://pf.kakao.com/_xbjxjhxb</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4357,7 +4325,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4368,7 +4336,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4377,13 +4345,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2444</v>
+        <v>4658</v>
       </c>
       <c r="Q42" t="n">
-        <v>3192</v>
+        <v>422</v>
       </c>
       <c r="R42" t="n">
-        <v>5636</v>
+        <v>5080</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4392,17 +4360,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1834367955</t>
+          <t>1895530050</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834367955</t>
+          <t>https://m.place.naver.com/place/1895530050</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4414,48 +4382,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>연청살롱</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7uoknow7@naver.com</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>헤리안</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>031-707-0426</t>
+          <t>0507-1381-7970</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 255 101호 연청살롱</t>
+          <t>경기도 성남시 분당구 판교역로 235 N동 1층 129호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/511640</t>
+          <t>https://www.instagram.com/herian_official</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4471,17 +4431,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1123</v>
+        <v>580</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>172</v>
       </c>
       <c r="R43" t="n">
-        <v>1126</v>
+        <v>752</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4490,17 +4450,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1930679218</t>
+          <t>1327869349</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930679218</t>
+          <t>https://m.place.naver.com/place/1327869349</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4512,44 +4472,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>고이비헤어</t>
+          <t>이철헤어커커 동판교테크노점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>qp6409@naver.com</t>
+          <t>kerker2327@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1448-3694</t>
+          <t>0507-1423-2326</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로255번길 9-22 A동 1층 115호</t>
+          <t>경기도 성남시 분당구 판교로 376 마크시티퍼플 3층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goibe_da_0000</t>
+          <t>http://leechulhairkerker.co.kr/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4560,7 +4520,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4569,13 +4529,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>256</v>
+        <v>2013</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="R44" t="n">
-        <v>262</v>
+        <v>2108</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4584,17 +4544,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1172147949</t>
+          <t>36465836</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172147949</t>
+          <t>https://m.place.naver.com/place/36465836</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4606,29 +4566,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>헤예가</t>
+          <t>르모아</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>brother2663@naver.com</t>
+          <t>beaux-arts-@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1338-6686</t>
+          <t>031-702-8797</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 하오개로 381 푸르지오하임 상가 202호 헤예가</t>
+          <t>경기도 성남시 분당구 판교로25번길 22-2 1층 르모아</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brother2663</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4638,12 +4598,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4663,13 +4623,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>363</v>
+        <v>3036</v>
       </c>
       <c r="Q45" t="n">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="R45" t="n">
-        <v>442</v>
+        <v>3172</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4678,17 +4638,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1685159975</t>
+          <t>1943090935</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685159975</t>
+          <t>https://m.place.naver.com/place/1943090935</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4700,29 +4660,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>미노크 판교 본점</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>day00ung@naver.com</t>
-        </is>
-      </c>
+          <t>아뜰리에조이</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1393-4669</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 18 1층 102호</t>
+          <t>경기도 성남시 분당구 산운로160번길 20-5 1층 101호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/menoke.official/?igshid=YmMyMTA2M2Y%3D</t>
+          <t>http://instagram.com/atelier.joy_</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4757,13 +4709,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2181</v>
+        <v>435</v>
       </c>
       <c r="Q46" t="n">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="R46" t="n">
-        <v>2322</v>
+        <v>451</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4772,17 +4724,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1260361427</t>
+          <t>1708579651</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260361427</t>
+          <t>https://m.place.naver.com/place/1708579651</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4794,29 +4746,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>미노크 판교 라이브러리</t>
+          <t>시유헤어스튜디오</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jtmina@naver.com</t>
+          <t>siyuhair@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1408-4669</t>
+          <t>0507-1491-7920</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로1길 18-1 1층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 53 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sssean_11</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4826,7 +4778,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4847,17 +4799,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>882</v>
+        <v>130</v>
       </c>
       <c r="Q47" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>1005</v>
+        <v>131</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4866,17 +4818,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1089065440</t>
+          <t>2075127898</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089065440</t>
+          <t>https://m.place.naver.com/place/2075127898</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4888,29 +4840,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 판교대장점</t>
+          <t>닥터헤어플러스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mslovegrzzz@naver.com</t>
+          <t>h_h0402_@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1447-7770</t>
+          <t>0507-1404-7739</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로4길 12-8 1층,지층</t>
+          <t>경기도 성남시 분당구 동판교로 52 제이스타빌딩 3층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pschair_pangyodaejang/</t>
+          <t>https://blog.naver.com/h_h0402_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4925,7 +4877,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4941,17 +4893,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>822</v>
+        <v>763</v>
       </c>
       <c r="Q48" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>907</v>
+        <v>763</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4960,17 +4912,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1089404633</t>
+          <t>741268087</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089404633</t>
+          <t>https://m.place.naver.com/place/741268087</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4982,34 +4934,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>컴인헤어</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>wydwlsdl@naver.com</t>
-        </is>
-      </c>
+          <t>예인헤어</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1444-9402</t>
+          <t>0507-1325-2333</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로1길 65 1층 컴인헤어</t>
+          <t>경기도 성남시 분당구 판교로 393 이지더원아파트정문 상가 114호 예인헤어</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wydwlsdl</t>
+          <t>https://www.facebook.com/profile.php?id=61574752066785</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5039,13 +4987,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>765</v>
+        <v>924</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>815</v>
+        <v>926</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5054,17 +5002,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1924589225</t>
+          <t>36768398</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924589225</t>
+          <t>https://m.place.naver.com/place/36768398</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5076,29 +5024,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>준오헤어 판교테크원점</t>
+          <t>이가자헤어비스 동판교점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>juno_tech1@naver.com</t>
+          <t>lkjdpg@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>070-8811-0605</t>
+          <t>031-8016-8322</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 2층</t>
+          <t>경기도 성남시 분당구 판교로 375 메가스페이스 2층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/juno_tech1</t>
+          <t>https://blog.naver.com/lkjdpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5129,17 +5077,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>18714</v>
+        <v>3530</v>
       </c>
       <c r="Q50" t="n">
-        <v>219</v>
+        <v>371</v>
       </c>
       <c r="R50" t="n">
-        <v>18933</v>
+        <v>3901</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5148,17 +5096,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1428947090</t>
+          <t>37171597</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428947090</t>
+          <t>https://m.place.naver.com/place/37171597</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5170,29 +5118,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>여백</t>
+          <t>컴인헤어</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sdhong88@naver.com</t>
+          <t>wydwlsdl@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1383-7066</t>
+          <t>0507-1444-9402</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로146번길 21 1층</t>
+          <t>경기도 성남시 분당구 판교공원로1길 65 1층 컴인헤어</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/y.bek_/</t>
+          <t>https://blog.naver.com/wydwlsdl</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5207,7 +5155,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5227,13 +5175,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="R51" t="n">
-        <v>788</v>
+        <v>824</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5242,17 +5190,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1635764333</t>
+          <t>1924589225</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1635764333</t>
+          <t>https://m.place.naver.com/place/1924589225</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5264,29 +5212,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>페어</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>mybcf@naver.com</t>
-        </is>
-      </c>
+          <t>오일리헤어</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1383-6737</t>
+          <t>031-711-2019</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 17-2 1층 101호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 16 엘포레상가 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/OILYHAIR_MINA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5296,7 +5240,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5317,17 +5261,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="Q52" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5336,17 +5280,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1614565528</t>
+          <t>1098582009</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614565528</t>
+          <t>https://m.place.naver.com/place/1098582009</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5358,29 +5302,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>라슈드헤어살롱</t>
+          <t>리미띠에헤어 분당판교점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>zzz_o_oz@naver.com</t>
+          <t>limitie22@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1425-2526</t>
+          <t>0507-1408-2150</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 5-21 103호(대장동)</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 판교타워 3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/s.been_lim</t>
+          <t>https://www.instagram.com/limitie_/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5415,13 +5359,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>378</v>
+        <v>2115</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>4853</v>
       </c>
       <c r="R53" t="n">
-        <v>385</v>
+        <v>6968</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5430,17 +5374,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1623639435</t>
+          <t>1490723364</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623639435</t>
+          <t>https://m.place.naver.com/place/1490723364</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5452,29 +5396,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>더레드도어헤어 대장동미용실</t>
+          <t>립헤어</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>090902_love@naver.com</t>
+          <t>libbhair@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1446-1544</t>
+          <t>0507-1493-0503</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로 92 푸리마타워 3층 304호</t>
+          <t>경기도 성남시 분당구 판교공원로5길 28 1층 립헤어</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/libb.hair</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5484,7 +5428,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5505,17 +5449,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1398</v>
+        <v>2193</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>234</v>
       </c>
       <c r="R54" t="n">
-        <v>1402</v>
+        <v>2427</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5524,17 +5468,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1122198740</t>
+          <t>1564288288</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1122198740</t>
+          <t>https://m.place.naver.com/place/1564288288</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5546,44 +5490,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>우브헤어</t>
+          <t>에쉬비헤어</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>qazwsx159925@naver.com</t>
+          <t>achevee@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1334-6341</t>
+          <t>0507-1351-6260</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 6-1 101호 우브헤어</t>
+          <t>경기도 성남시 분당구 판교공원로2길 65 1층 102호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://01072726341.tshome.co.kr/</t>
+          <t>https://blog.naver.com/achevee</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5599,17 +5543,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>736</v>
+        <v>882</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="R55" t="n">
-        <v>762</v>
+        <v>921</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5618,17 +5562,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1080085479</t>
+          <t>1370317722</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1080085479</t>
+          <t>https://m.place.naver.com/place/1370317722</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5640,29 +5584,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에이치플레이스 그레이츠판교역점</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>woosy0225@naver.com</t>
-        </is>
-      </c>
+          <t>준오헤어 서판교점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1320-5923</t>
+          <t>0507-1332-0610</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 그레이츠 판교 2층 201-2호</t>
+          <t>경기도 성남시 분당구 운중로 249 더제이에스빌딩 2층 준오헤어 서판교점</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/h.place_official</t>
+          <t>https://www.instagram.com/junospg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5697,13 +5637,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>6094</v>
+        <v>13082</v>
       </c>
       <c r="Q56" t="n">
-        <v>607</v>
+        <v>480</v>
       </c>
       <c r="R56" t="n">
-        <v>6701</v>
+        <v>13562</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5712,17 +5652,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1774601367</t>
+          <t>1391913826</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774601367</t>
+          <t>https://m.place.naver.com/place/1391913826</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5734,29 +5674,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>보니따라움</t>
+          <t>준오헤어 판교테크원점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>socoolar@naver.com</t>
+          <t>juno_tech1@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1426-4648</t>
+          <t>070-8811-0605</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 17 1층 보니따라움</t>
+          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 2층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/socoolar</t>
+          <t>https://blog.naver.com/juno_tech1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5791,13 +5731,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3068</v>
+        <v>18801</v>
       </c>
       <c r="Q57" t="n">
-        <v>119</v>
+        <v>230</v>
       </c>
       <c r="R57" t="n">
-        <v>3187</v>
+        <v>19031</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5806,17 +5746,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1663607000</t>
+          <t>1428947090</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663607000</t>
+          <t>https://m.place.naver.com/place/1428947090</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5828,29 +5768,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>제니스튜디오 판교점</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>dkyun22@naver.com</t>
-        </is>
-      </c>
+          <t>모디아스헤어</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1385-8458</t>
+          <t>0507-1395-3849</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로10번길 10-4 1층</t>
+          <t>경기도 성남시 분당구 판교역로192번길 16 203호 2층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dkyun22</t>
+          <t>https://www.instagram.com/modias_twohands</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5865,7 +5801,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5885,13 +5821,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2345</v>
+        <v>336</v>
       </c>
       <c r="Q58" t="n">
-        <v>772</v>
+        <v>59</v>
       </c>
       <c r="R58" t="n">
-        <v>3117</v>
+        <v>395</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5900,17 +5836,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1480897275</t>
+          <t>1531553456</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1480897275</t>
+          <t>https://m.place.naver.com/place/1531553456</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5922,34 +5858,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>오아헤어 판교점</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>scandjy@naver.com</t>
-        </is>
-      </c>
+          <t>준오헤어 판교알파돔시티점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>031-701-2877</t>
+          <t>0507-1389-0611</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로25번길 12-1 1층 오아헤어</t>
+          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 준오헤어</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.a_hair</t>
+          <t>http://junohair.com/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5979,13 +5911,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1907</v>
+        <v>33696</v>
       </c>
       <c r="Q59" t="n">
-        <v>133</v>
+        <v>1373</v>
       </c>
       <c r="R59" t="n">
-        <v>2040</v>
+        <v>35069</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5994,17 +5926,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1188163002</t>
+          <t>1377606557</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1188163002</t>
+          <t>https://m.place.naver.com/place/1377606557</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6016,39 +5948,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>헤어하우스606 판교역점</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>zzz_o_oz@naver.com</t>
-        </is>
-      </c>
+          <t>쌤시크 서판교점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1333-7268</t>
+          <t>0507-1469-3543</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 푸르지오월드마크 상가동 1층 1-58호</t>
+          <t>경기도 성남시 분당구 운중로 135 더원스퀘어 2층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JWuxdn/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6064,7 +5992,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6073,13 +6001,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>337</v>
+        <v>1870</v>
       </c>
       <c r="Q60" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="R60" t="n">
-        <v>382</v>
+        <v>1946</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6088,17 +6016,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1005163873</t>
+          <t>1303041625</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005163873</t>
+          <t>https://m.place.naver.com/place/1303041625</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6110,34 +6038,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>차홍룸 판교점</t>
+          <t>박승철헤어스투디오 판교대장점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>chahong1@naver.com</t>
+          <t>chaebboongs@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1337-4752</t>
+          <t>0507-1447-7770</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 상가1층 1105호</t>
+          <t>경기도 성남시 분당구 판교대장로4길 12-8 1층,지층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/chahongofficial</t>
+          <t>https://www.instagram.com/pschair_pangyodaejang/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6147,7 +6075,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6167,13 +6095,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>13854</v>
+        <v>832</v>
       </c>
       <c r="Q61" t="n">
-        <v>298</v>
+        <v>87</v>
       </c>
       <c r="R61" t="n">
-        <v>14152</v>
+        <v>919</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6182,17 +6110,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1617942139</t>
+          <t>1089404633</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1617942139</t>
+          <t>https://m.place.naver.com/place/1089404633</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6204,29 +6132,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>순수 더블트리 바이 힐튼 서울 판교점</t>
+          <t>공시하 판교점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>dkfk2685@naver.com</t>
+          <t>gongsiha@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1305-1379</t>
+          <t>0507-1349-7513</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로 26 레지던스동 G층 3호 순수 미용실</t>
+          <t>경기도 성남시 분당구 판교공원로1길 47 1층 공시하</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soonsoo_hilton</t>
+          <t>https://blog.naver.com/gongsiha/223367774442</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6241,7 +6169,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6261,13 +6189,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>310</v>
+        <v>2478</v>
       </c>
       <c r="Q62" t="n">
-        <v>109</v>
+        <v>3380</v>
       </c>
       <c r="R62" t="n">
-        <v>419</v>
+        <v>5858</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6276,17 +6204,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1403230950</t>
+          <t>1834367955</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403230950</t>
+          <t>https://m.place.naver.com/place/1834367955</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6229,7 @@
           <t>나이스가이 서판교점</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>zzz_o_oz@naver.com</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6380,7 +6304,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6392,29 +6316,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>모디아스헤어</t>
+          <t>궁서채 서현역점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hyacinthcmsh@naver.com</t>
+          <t>muadhair@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1395-3849</t>
+          <t>0507-1467-2069</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 16 203호 2층</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 3층 302호 궁서채 서현역점</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/modias_twohands</t>
+          <t>https://blog.naver.com/muadhair</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6429,7 +6353,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6445,17 +6369,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>321</v>
+        <v>409</v>
       </c>
       <c r="Q64" t="n">
-        <v>54</v>
+        <v>1335</v>
       </c>
       <c r="R64" t="n">
-        <v>375</v>
+        <v>1744</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6464,17 +6388,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1531553456</t>
+          <t>1278312550</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1531553456</t>
+          <t>https://m.place.naver.com/place/1278312550</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6486,29 +6410,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>아센티 더 판교</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>robbiedhu@naver.com</t>
-        </is>
-      </c>
+          <t>와이오유 판교점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1342-4783</t>
+          <t>0507-1406-1479</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 10 라스트리트 타워 1동 2층 212호</t>
+          <t>경기도 성남시 분당구 판교역로18번길 18</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/asenti_the_pangyo</t>
+          <t>https://www.youtube.com/c/와이오유yousalon</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6543,13 +6463,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>952</v>
+        <v>10115</v>
       </c>
       <c r="Q65" t="n">
-        <v>62</v>
+        <v>811</v>
       </c>
       <c r="R65" t="n">
-        <v>1014</v>
+        <v>10926</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6558,17 +6478,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1693297113</t>
+          <t>35194802</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693297113</t>
+          <t>https://m.place.naver.com/place/35194802</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6580,29 +6500,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>토니앤가이 판교점</t>
+          <t>히로</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hair121212@naver.com</t>
+          <t>slk35o@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>031-703-7577</t>
+          <t>0507-1458-9667</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 1층</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-17 1층 101호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hair121212</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6612,12 +6532,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6637,13 +6557,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>4167</v>
+        <v>165</v>
       </c>
       <c r="Q66" t="n">
-        <v>181</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>4348</v>
+        <v>167</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6652,17 +6572,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1891585241</t>
+          <t>1776884469</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1891585241</t>
+          <t>https://m.place.naver.com/place/1776884469</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6674,29 +6594,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>살롱 J</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>nancy866@naver.com</t>
-        </is>
-      </c>
+          <t>라슈드헤어살롱</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1377-4462</t>
+          <t>0507-1425-2526</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 1층 101호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 5-21 103호(대장동)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/s.been_lim</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6706,7 +6622,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6727,17 +6643,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>165</v>
+        <v>379</v>
       </c>
       <c r="Q67" t="n">
-        <v>217</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6746,17 +6662,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1886976990</t>
+          <t>1623639435</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886976990</t>
+          <t>https://m.place.naver.com/place/1623639435</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6768,34 +6684,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>준오헤어 판교알파돔시티점</t>
+          <t>오아헤어 판교점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>junopg0605@naver.com</t>
+          <t>scandjy@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1389-0611</t>
+          <t>031-701-2877</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 152 알파돔타워 3층 준오헤어</t>
+          <t>경기도 성남시 분당구 판교로25번길 12-1 1층 오아헤어</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://junohair.com/</t>
+          <t>https://www.instagram.com/o.a_hair</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6825,13 +6741,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>33583</v>
+        <v>1906</v>
       </c>
       <c r="Q68" t="n">
-        <v>1369</v>
+        <v>133</v>
       </c>
       <c r="R68" t="n">
-        <v>34952</v>
+        <v>2039</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6840,17 +6756,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1377606557</t>
+          <t>1188163002</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377606557</t>
+          <t>https://m.place.naver.com/place/1188163002</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6862,29 +6778,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>헤어마드 판교점</t>
+          <t>꼼나나비앙 판교점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>minisu_1@naver.com</t>
+          <t>comme_pangyo@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1342-6828</t>
+          <t>0507-1332-8195</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 지1층 비107호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 10 라스트리트 1동 2층 224호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/commenanabien_pangyo/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6894,7 +6810,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6915,17 +6831,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1091</v>
+        <v>5973</v>
       </c>
       <c r="Q69" t="n">
-        <v>62</v>
+        <v>379</v>
       </c>
       <c r="R69" t="n">
-        <v>1153</v>
+        <v>6352</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6934,51 +6850,51 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1640957766</t>
+          <t>1867649955</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1640957766</t>
+          <t>https://m.place.naver.com/place/1867649955</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>마제스티바버샵 현대백화점 판교점</t>
+          <t>꾸밈 판교역점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>fcgaon@naver.com</t>
+          <t>jooa_design@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>031-5170-2631</t>
+          <t>031-702-7700</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로146번길 20 6F</t>
+          <t>경기도 성남시 분당구 판교역로 180 2층 201호 꾸밈 판교역점</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fcgaon</t>
+          <t>https://blog.naver.com/jooa_design</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7013,13 +6929,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1342</v>
+        <v>3785</v>
       </c>
       <c r="Q70" t="n">
-        <v>20</v>
+        <v>1840</v>
       </c>
       <c r="R70" t="n">
-        <v>1362</v>
+        <v>5625</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7028,17 +6944,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>37197627</t>
+          <t>1107338199</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37197627</t>
+          <t>https://m.place.naver.com/place/1107338199</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7050,29 +6966,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>덕테일 바버샵</t>
+          <t>골든컷츠바버샵</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>amorsino@naver.com</t>
+          <t>k930225@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1397-4798</t>
+          <t>0507-1471-2043</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 34 1층</t>
+          <t>경기도 성남시 분당구 판교역로 6-4 1층 골든컷츠바버샵</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/goldencuts21</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7082,7 +6998,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7103,17 +7019,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1313</v>
+        <v>1159</v>
       </c>
       <c r="Q71" t="n">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="R71" t="n">
-        <v>1493</v>
+        <v>1240</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7122,17 +7038,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1086675542</t>
+          <t>1401377381</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1086675542</t>
+          <t>https://m.place.naver.com/place/1401377381</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7144,34 +7060,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>킹스백바버샵 본점</t>
+          <t>덕테일 바버샵</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>babmattrip@naver.com</t>
+          <t>amorsino@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1305-4798</t>
+          <t>0507-1397-4798</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 6-8 1층 킹스백바버샵 본점</t>
+          <t>경기도 성남시 분당구 판교역로2번길 34 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://kingsbag.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7181,7 +7097,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7197,17 +7113,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2243</v>
+        <v>1330</v>
       </c>
       <c r="Q72" t="n">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="R72" t="n">
-        <v>2343</v>
+        <v>1512</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7216,17 +7132,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1749373340</t>
+          <t>1086675542</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1749373340</t>
+          <t>https://m.place.naver.com/place/1086675542</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7295,13 +7211,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1602</v>
+        <v>1610</v>
       </c>
       <c r="Q73" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R73" t="n">
-        <v>1723</v>
+        <v>1732</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7320,7 +7236,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7332,29 +7248,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>애프터선데이클럽</t>
+          <t>뮤트</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>diana805@naver.com</t>
+          <t>victoryace89@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1320-3766</t>
+          <t>0507-1311-7624</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 19-17 102호</t>
+          <t>경기도 성남시 분당구 동판교로52번길 13-9 1층 뮤트 바버샵</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aftersundayclub</t>
+          <t>https://www.instagram.com/mewtbarbershop/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7389,13 +7305,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>744</v>
+        <v>15</v>
       </c>
       <c r="Q74" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>793</v>
+        <v>18</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7404,17 +7320,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1466044568</t>
+          <t>2002168528</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466044568</t>
+          <t>https://m.place.naver.com/place/2002168528</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7426,29 +7342,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>골든컷츠바버샵</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>k930225@naver.com</t>
-        </is>
-      </c>
+          <t>애프터선데이클럽</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1471-2043</t>
+          <t>0507-1320-3766</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 6-4 1층 골든컷츠바버샵</t>
+          <t>경기도 성남시 분당구 동판교로52번길 19-17 102호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://instagram.com/goldencuts21</t>
+          <t>https://www.instagram.com/aftersundayclub</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7483,13 +7395,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1158</v>
+        <v>748</v>
       </c>
       <c r="Q75" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="R75" t="n">
-        <v>1239</v>
+        <v>799</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7498,17 +7410,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1401377381</t>
+          <t>1466044568</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1401377381</t>
+          <t>https://m.place.naver.com/place/1466044568</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7520,44 +7432,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>맨앤독바버샵</t>
+          <t>킹스백바버샵 본점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>photoby_jisoo@naver.com</t>
+          <t>babmattrip@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1320-3346</t>
+          <t>0507-1305-4798</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로52번길 15 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 6-8 1층 킹스백바버샵 본점</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mandog_barbershop</t>
+          <t>https://kingsbag.co.kr</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7577,13 +7489,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>314</v>
+        <v>2245</v>
       </c>
       <c r="Q76" t="n">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="R76" t="n">
-        <v>325</v>
+        <v>2344</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7592,17 +7504,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1861529692</t>
+          <t>1749373340</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1861529692</t>
+          <t>https://m.place.naver.com/place/1749373340</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
